--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -6618,7 +6618,7 @@
         <v>110860268</v>
       </c>
       <c r="B48" t="n">
-        <v>88095</v>
+        <v>88102</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11082,6 +11082,1756 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>121680859</v>
+      </c>
+      <c r="B90" t="n">
+        <v>92039</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>573519</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6659018</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>121680860</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91998</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Stormossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>573326</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6658892</v>
+      </c>
+      <c r="S91" t="n">
+        <v>4</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>121680775</v>
+      </c>
+      <c r="B92" t="n">
+        <v>90228</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>573420</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6658800</v>
+      </c>
+      <c r="S92" t="n">
+        <v>4</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>121680774</v>
+      </c>
+      <c r="B93" t="n">
+        <v>92039</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>573413</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6658670</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>121680772</v>
+      </c>
+      <c r="B94" t="n">
+        <v>92039</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>573445</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6658922</v>
+      </c>
+      <c r="S94" t="n">
+        <v>3</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>121680773</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91998</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>573423</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6658673</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>121681090</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78642</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>573424</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6659001</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>121680776</v>
+      </c>
+      <c r="B97" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>573374</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6658857</v>
+      </c>
+      <c r="S97" t="n">
+        <v>4</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>121681666</v>
+      </c>
+      <c r="B98" t="n">
+        <v>58061</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>573385</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6658886</v>
+      </c>
+      <c r="S98" t="n">
+        <v>4</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-04-24</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>06:59</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Jannik Jansons</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>121680861</v>
+      </c>
+      <c r="B99" t="n">
+        <v>92039</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>573378</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6658802</v>
+      </c>
+      <c r="S99" t="n">
+        <v>4</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>121679577</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57785</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>573462</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6658905</v>
+      </c>
+      <c r="S100" t="n">
+        <v>2</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Jake Bull</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>121681091</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78642</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>573384</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6658904</v>
+      </c>
+      <c r="S101" t="n">
+        <v>3</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2023-10-20</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Carin von Köhler</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>121680761</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92039</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Stormossen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>573322</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6658875</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>121680858</v>
+      </c>
+      <c r="B103" t="n">
+        <v>92004</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Långheden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>573396</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6659037</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Västerfärnebo</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2023-10-23</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Signe Vendike</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Rejlers - Sala till Avesta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121680774</v>
+        <v>121681666</v>
       </c>
       <c r="B90" t="n">
-        <v>92039</v>
+        <v>58061</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11100,21 +11100,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>103055</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11122,9 +11122,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11133,13 +11133,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573413</v>
+        <v>573385</v>
       </c>
       <c r="R90" t="n">
-        <v>6658670</v>
+        <v>6658886</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11163,22 +11163,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11209,7 +11209,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121680776</v>
+        <v>121680858</v>
       </c>
       <c r="B91" t="n">
         <v>92004</v>
@@ -11244,12 +11244,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573374</v>
+        <v>573396</v>
       </c>
       <c r="R91" t="n">
-        <v>6658857</v>
+        <v>6659037</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121681090</v>
+        <v>121680859</v>
       </c>
       <c r="B92" t="n">
-        <v>78642</v>
+        <v>92039</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11346,25 +11346,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11383,13 +11383,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573424</v>
+        <v>573519</v>
       </c>
       <c r="R92" t="n">
-        <v>6659001</v>
+        <v>6659018</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11459,7 +11459,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121680861</v>
+        <v>121680774</v>
       </c>
       <c r="B93" t="n">
         <v>92039</v>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573378</v>
+        <v>573413</v>
       </c>
       <c r="R93" t="n">
-        <v>6658802</v>
+        <v>6658670</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121680761</v>
+        <v>121681091</v>
       </c>
       <c r="B94" t="n">
-        <v>92039</v>
+        <v>78642</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11596,25 +11596,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11624,22 +11624,22 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573322</v>
+        <v>573384</v>
       </c>
       <c r="R94" t="n">
-        <v>6658875</v>
+        <v>6658904</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11663,22 +11663,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680859</v>
+        <v>121680776</v>
       </c>
       <c r="B95" t="n">
-        <v>92039</v>
+        <v>92004</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,25 +11721,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11758,13 +11758,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573519</v>
+        <v>573374</v>
       </c>
       <c r="R95" t="n">
-        <v>6659018</v>
+        <v>6658857</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121681666</v>
+        <v>121681090</v>
       </c>
       <c r="B96" t="n">
-        <v>58061</v>
+        <v>78642</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11846,25 +11846,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103055</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11872,9 +11872,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573385</v>
+        <v>573424</v>
       </c>
       <c r="R96" t="n">
-        <v>6658886</v>
+        <v>6659001</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680772</v>
+        <v>121680775</v>
       </c>
       <c r="B97" t="n">
-        <v>92039</v>
+        <v>90228</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11971,25 +11971,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12008,13 +12008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573445</v>
+        <v>573420</v>
       </c>
       <c r="R97" t="n">
-        <v>6658922</v>
+        <v>6658800</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680775</v>
+        <v>121680772</v>
       </c>
       <c r="B98" t="n">
-        <v>90228</v>
+        <v>92039</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12096,25 +12096,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573420</v>
+        <v>573445</v>
       </c>
       <c r="R98" t="n">
-        <v>6658800</v>
+        <v>6658922</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680858</v>
+        <v>121680773</v>
       </c>
       <c r="B99" t="n">
-        <v>92004</v>
+        <v>91998</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12221,35 +12221,35 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573396</v>
+        <v>573423</v>
       </c>
       <c r="R99" t="n">
-        <v>6659037</v>
+        <v>6658673</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12334,10 +12334,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121681091</v>
+        <v>121680761</v>
       </c>
       <c r="B100" t="n">
-        <v>78642</v>
+        <v>92039</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12346,25 +12346,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -12374,22 +12374,22 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573384</v>
+        <v>573322</v>
       </c>
       <c r="R100" t="n">
-        <v>6658904</v>
+        <v>6658875</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12413,22 +12413,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121679577</v>
+        <v>121680860</v>
       </c>
       <c r="B101" t="n">
-        <v>57785</v>
+        <v>91998</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103001</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12497,24 +12497,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573462</v>
+        <v>573326</v>
       </c>
       <c r="R101" t="n">
-        <v>6658905</v>
+        <v>6658892</v>
       </c>
       <c r="S101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12538,22 +12538,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680773</v>
+        <v>121680861</v>
       </c>
       <c r="B102" t="n">
-        <v>91998</v>
+        <v>92039</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573423</v>
+        <v>573378</v>
       </c>
       <c r="R102" t="n">
-        <v>6658673</v>
+        <v>6658802</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121680860</v>
+        <v>121679577</v>
       </c>
       <c r="B103" t="n">
-        <v>91998</v>
+        <v>57785</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4362</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12747,24 +12747,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573326</v>
+        <v>573462</v>
       </c>
       <c r="R103" t="n">
-        <v>6658892</v>
+        <v>6658905</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121680858</v>
+        <v>121679577</v>
       </c>
       <c r="B91" t="n">
-        <v>92004</v>
+        <v>57785</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11221,35 +11221,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573396</v>
+        <v>573462</v>
       </c>
       <c r="R91" t="n">
-        <v>6659037</v>
+        <v>6658905</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121680859</v>
+        <v>121680858</v>
       </c>
       <c r="B92" t="n">
-        <v>92039</v>
+        <v>92004</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11346,30 +11346,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11383,10 +11383,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573519</v>
+        <v>573396</v>
       </c>
       <c r="R92" t="n">
-        <v>6659018</v>
+        <v>6659037</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11459,10 +11459,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121680774</v>
+        <v>121680775</v>
       </c>
       <c r="B93" t="n">
-        <v>92039</v>
+        <v>90228</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11471,25 +11471,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573413</v>
+        <v>573420</v>
       </c>
       <c r="R93" t="n">
-        <v>6658670</v>
+        <v>6658800</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121681091</v>
+        <v>121680776</v>
       </c>
       <c r="B94" t="n">
-        <v>78642</v>
+        <v>92004</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11600,21 +11600,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11633,13 +11633,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573384</v>
+        <v>573374</v>
       </c>
       <c r="R94" t="n">
-        <v>6658904</v>
+        <v>6658857</v>
       </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11663,22 +11663,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680776</v>
+        <v>121680860</v>
       </c>
       <c r="B95" t="n">
-        <v>92004</v>
+        <v>91998</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,25 +11721,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11749,19 +11749,19 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573374</v>
+        <v>573326</v>
       </c>
       <c r="R95" t="n">
-        <v>6658857</v>
+        <v>6658892</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121681090</v>
+        <v>121680773</v>
       </c>
       <c r="B96" t="n">
-        <v>78642</v>
+        <v>91998</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11846,25 +11846,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573424</v>
+        <v>573423</v>
       </c>
       <c r="R96" t="n">
-        <v>6659001</v>
+        <v>6658673</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680775</v>
+        <v>121680761</v>
       </c>
       <c r="B97" t="n">
-        <v>90228</v>
+        <v>92039</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11971,25 +11971,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11999,22 +11999,22 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573420</v>
+        <v>573322</v>
       </c>
       <c r="R97" t="n">
-        <v>6658800</v>
+        <v>6658875</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680772</v>
+        <v>121681090</v>
       </c>
       <c r="B98" t="n">
-        <v>92039</v>
+        <v>78642</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12096,25 +12096,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573445</v>
+        <v>573424</v>
       </c>
       <c r="R98" t="n">
-        <v>6658922</v>
+        <v>6659001</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12163,22 +12163,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680773</v>
+        <v>121680774</v>
       </c>
       <c r="B99" t="n">
-        <v>91998</v>
+        <v>92039</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12225,21 +12225,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573423</v>
+        <v>573413</v>
       </c>
       <c r="R99" t="n">
-        <v>6658673</v>
+        <v>6658670</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12334,7 +12334,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680761</v>
+        <v>121680861</v>
       </c>
       <c r="B100" t="n">
         <v>92039</v>
@@ -12379,17 +12379,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573322</v>
+        <v>573378</v>
       </c>
       <c r="R100" t="n">
-        <v>6658875</v>
+        <v>6658802</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680860</v>
+        <v>121680772</v>
       </c>
       <c r="B101" t="n">
-        <v>91998</v>
+        <v>92039</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12499,22 +12499,22 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573326</v>
+        <v>573445</v>
       </c>
       <c r="R101" t="n">
-        <v>6658892</v>
+        <v>6658922</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12584,7 +12584,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680861</v>
+        <v>121680859</v>
       </c>
       <c r="B102" t="n">
         <v>92039</v>
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573378</v>
+        <v>573519</v>
       </c>
       <c r="R102" t="n">
-        <v>6658802</v>
+        <v>6659018</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121679577</v>
+        <v>121681091</v>
       </c>
       <c r="B103" t="n">
-        <v>57785</v>
+        <v>78642</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12721,25 +12721,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12747,9 +12747,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573462</v>
+        <v>573384</v>
       </c>
       <c r="R103" t="n">
-        <v>6658905</v>
+        <v>6658904</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121681666</v>
+        <v>121680858</v>
       </c>
       <c r="B90" t="n">
-        <v>58061</v>
+        <v>92004</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11096,35 +11096,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103055</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11133,13 +11133,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573385</v>
+        <v>573396</v>
       </c>
       <c r="R90" t="n">
-        <v>6658886</v>
+        <v>6659037</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11163,22 +11163,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B91" t="n">
-        <v>57785</v>
+        <v>58061</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11225,21 +11225,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R91" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S91" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121680858</v>
+        <v>121680859</v>
       </c>
       <c r="B92" t="n">
-        <v>92004</v>
+        <v>92039</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11346,30 +11346,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11383,10 +11383,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573396</v>
+        <v>573519</v>
       </c>
       <c r="R92" t="n">
-        <v>6659037</v>
+        <v>6659018</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680860</v>
+        <v>121680772</v>
       </c>
       <c r="B95" t="n">
-        <v>91998</v>
+        <v>92039</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11725,21 +11725,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11749,22 +11749,22 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573326</v>
+        <v>573445</v>
       </c>
       <c r="R95" t="n">
-        <v>6658892</v>
+        <v>6658922</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680761</v>
+        <v>121680860</v>
       </c>
       <c r="B97" t="n">
-        <v>92039</v>
+        <v>91998</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12008,13 +12008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573322</v>
+        <v>573326</v>
       </c>
       <c r="R97" t="n">
-        <v>6658875</v>
+        <v>6658892</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121681090</v>
+        <v>121680861</v>
       </c>
       <c r="B98" t="n">
-        <v>78642</v>
+        <v>92039</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12096,25 +12096,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573424</v>
+        <v>573378</v>
       </c>
       <c r="R98" t="n">
-        <v>6659001</v>
+        <v>6658802</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12163,22 +12163,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680774</v>
+        <v>121681091</v>
       </c>
       <c r="B99" t="n">
-        <v>92039</v>
+        <v>78642</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12221,25 +12221,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12258,13 +12258,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573413</v>
+        <v>573384</v>
       </c>
       <c r="R99" t="n">
-        <v>6658670</v>
+        <v>6658904</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12288,22 +12288,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12334,7 +12334,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680861</v>
+        <v>121680761</v>
       </c>
       <c r="B100" t="n">
         <v>92039</v>
@@ -12379,17 +12379,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573378</v>
+        <v>573322</v>
       </c>
       <c r="R100" t="n">
-        <v>6658802</v>
+        <v>6658875</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12459,7 +12459,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680772</v>
+        <v>121680774</v>
       </c>
       <c r="B101" t="n">
         <v>92039</v>
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573445</v>
+        <v>573413</v>
       </c>
       <c r="R101" t="n">
-        <v>6658922</v>
+        <v>6658670</v>
       </c>
       <c r="S101" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680859</v>
+        <v>121679577</v>
       </c>
       <c r="B102" t="n">
-        <v>92039</v>
+        <v>57785</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5966</v>
+        <v>103001</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12622,9 +12622,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573519</v>
+        <v>573462</v>
       </c>
       <c r="R102" t="n">
-        <v>6659018</v>
+        <v>6658905</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,7 +12709,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121681091</v>
+        <v>121681090</v>
       </c>
       <c r="B103" t="n">
         <v>78642</v>
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573384</v>
+        <v>573424</v>
       </c>
       <c r="R103" t="n">
-        <v>6658904</v>
+        <v>6659001</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121680858</v>
+        <v>121679577</v>
       </c>
       <c r="B90" t="n">
-        <v>92004</v>
+        <v>57785</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11096,35 +11096,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>103001</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11133,13 +11133,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573396</v>
+        <v>573462</v>
       </c>
       <c r="R90" t="n">
-        <v>6659037</v>
+        <v>6658905</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11163,22 +11163,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121681666</v>
+        <v>121680775</v>
       </c>
       <c r="B91" t="n">
-        <v>58061</v>
+        <v>90228</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11221,25 +11221,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103055</v>
+        <v>256703</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11247,9 +11247,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,10 +11258,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573385</v>
+        <v>573420</v>
       </c>
       <c r="R91" t="n">
-        <v>6658886</v>
+        <v>6658800</v>
       </c>
       <c r="S91" t="n">
         <v>4</v>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121680859</v>
+        <v>121681666</v>
       </c>
       <c r="B92" t="n">
-        <v>92039</v>
+        <v>58061</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11350,21 +11350,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5966</v>
+        <v>103055</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11372,9 +11372,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11383,13 +11383,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573519</v>
+        <v>573385</v>
       </c>
       <c r="R92" t="n">
-        <v>6659018</v>
+        <v>6658886</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11459,10 +11459,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121680775</v>
+        <v>121680776</v>
       </c>
       <c r="B93" t="n">
-        <v>90228</v>
+        <v>92004</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11475,21 +11475,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11508,10 +11508,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573420</v>
+        <v>573374</v>
       </c>
       <c r="R93" t="n">
-        <v>6658800</v>
+        <v>6658857</v>
       </c>
       <c r="S93" t="n">
         <v>4</v>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121680776</v>
+        <v>121680774</v>
       </c>
       <c r="B94" t="n">
-        <v>92004</v>
+        <v>92039</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11596,25 +11596,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11633,13 +11633,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573374</v>
+        <v>573413</v>
       </c>
       <c r="R94" t="n">
-        <v>6658857</v>
+        <v>6658670</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680772</v>
+        <v>121681091</v>
       </c>
       <c r="B95" t="n">
-        <v>92039</v>
+        <v>78642</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,25 +11721,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573445</v>
+        <v>573384</v>
       </c>
       <c r="R95" t="n">
-        <v>6658922</v>
+        <v>6658904</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -11788,22 +11788,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121680773</v>
+        <v>121681090</v>
       </c>
       <c r="B96" t="n">
-        <v>91998</v>
+        <v>78642</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11846,25 +11846,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573423</v>
+        <v>573424</v>
       </c>
       <c r="R96" t="n">
-        <v>6658673</v>
+        <v>6659001</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680860</v>
+        <v>121680861</v>
       </c>
       <c r="B97" t="n">
-        <v>91998</v>
+        <v>92039</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -12004,14 +12004,14 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573326</v>
+        <v>573378</v>
       </c>
       <c r="R97" t="n">
-        <v>6658892</v>
+        <v>6658802</v>
       </c>
       <c r="S97" t="n">
         <v>4</v>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12084,7 +12084,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680861</v>
+        <v>121680761</v>
       </c>
       <c r="B98" t="n">
         <v>92039</v>
@@ -12129,17 +12129,17 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573378</v>
+        <v>573322</v>
       </c>
       <c r="R98" t="n">
-        <v>6658802</v>
+        <v>6658875</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121681091</v>
+        <v>121680860</v>
       </c>
       <c r="B99" t="n">
-        <v>78642</v>
+        <v>91998</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12221,25 +12221,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12249,22 +12249,22 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573384</v>
+        <v>573326</v>
       </c>
       <c r="R99" t="n">
-        <v>6658904</v>
+        <v>6658892</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12288,22 +12288,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12334,7 +12334,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680761</v>
+        <v>121680859</v>
       </c>
       <c r="B100" t="n">
         <v>92039</v>
@@ -12379,14 +12379,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573322</v>
+        <v>573519</v>
       </c>
       <c r="R100" t="n">
-        <v>6658875</v>
+        <v>6659018</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680774</v>
+        <v>121680773</v>
       </c>
       <c r="B101" t="n">
-        <v>92039</v>
+        <v>91998</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573413</v>
+        <v>573423</v>
       </c>
       <c r="R101" t="n">
-        <v>6658670</v>
+        <v>6658673</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121679577</v>
+        <v>121680858</v>
       </c>
       <c r="B102" t="n">
-        <v>57785</v>
+        <v>92004</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12596,35 +12596,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103001</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573462</v>
+        <v>573396</v>
       </c>
       <c r="R102" t="n">
-        <v>6658905</v>
+        <v>6659037</v>
       </c>
       <c r="S102" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121681090</v>
+        <v>121680772</v>
       </c>
       <c r="B103" t="n">
-        <v>78642</v>
+        <v>92039</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12721,25 +12721,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573424</v>
+        <v>573445</v>
       </c>
       <c r="R103" t="n">
-        <v>6659001</v>
+        <v>6658922</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B90" t="n">
-        <v>57785</v>
+        <v>58061</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11100,21 +11100,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11133,13 +11133,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R90" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11163,22 +11163,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121680775</v>
+        <v>121680773</v>
       </c>
       <c r="B91" t="n">
-        <v>90228</v>
+        <v>91998</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11221,25 +11221,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>256703</v>
+        <v>4362</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573420</v>
+        <v>573423</v>
       </c>
       <c r="R91" t="n">
-        <v>6658800</v>
+        <v>6658673</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121681666</v>
+        <v>121679577</v>
       </c>
       <c r="B92" t="n">
-        <v>58061</v>
+        <v>57785</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11350,21 +11350,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11383,13 +11383,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573385</v>
+        <v>573462</v>
       </c>
       <c r="R92" t="n">
-        <v>6658886</v>
+        <v>6658905</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11459,10 +11459,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121680776</v>
+        <v>121681091</v>
       </c>
       <c r="B93" t="n">
-        <v>92004</v>
+        <v>78642</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11475,21 +11475,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573374</v>
+        <v>573384</v>
       </c>
       <c r="R93" t="n">
-        <v>6658857</v>
+        <v>6658904</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11538,22 +11538,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121681091</v>
+        <v>121680858</v>
       </c>
       <c r="B95" t="n">
-        <v>78642</v>
+        <v>92004</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11725,31 +11725,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11758,13 +11758,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573384</v>
+        <v>573396</v>
       </c>
       <c r="R95" t="n">
-        <v>6658904</v>
+        <v>6659037</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11788,22 +11788,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11959,7 +11959,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680861</v>
+        <v>121680772</v>
       </c>
       <c r="B97" t="n">
         <v>92039</v>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12008,13 +12008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573378</v>
+        <v>573445</v>
       </c>
       <c r="R97" t="n">
-        <v>6658802</v>
+        <v>6658922</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680761</v>
+        <v>121680775</v>
       </c>
       <c r="B98" t="n">
-        <v>92039</v>
+        <v>90228</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12096,25 +12096,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12124,22 +12124,22 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573322</v>
+        <v>573420</v>
       </c>
       <c r="R98" t="n">
-        <v>6658875</v>
+        <v>6658800</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680860</v>
+        <v>121680776</v>
       </c>
       <c r="B99" t="n">
-        <v>91998</v>
+        <v>92004</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12221,25 +12221,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12249,19 +12249,19 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573326</v>
+        <v>573374</v>
       </c>
       <c r="R99" t="n">
-        <v>6658892</v>
+        <v>6658857</v>
       </c>
       <c r="S99" t="n">
         <v>4</v>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12334,7 +12334,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680859</v>
+        <v>121680761</v>
       </c>
       <c r="B100" t="n">
         <v>92039</v>
@@ -12379,14 +12379,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573519</v>
+        <v>573322</v>
       </c>
       <c r="R100" t="n">
-        <v>6659018</v>
+        <v>6658875</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680773</v>
+        <v>121680861</v>
       </c>
       <c r="B101" t="n">
-        <v>91998</v>
+        <v>92039</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573423</v>
+        <v>573378</v>
       </c>
       <c r="R101" t="n">
-        <v>6658673</v>
+        <v>6658802</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680858</v>
+        <v>121680860</v>
       </c>
       <c r="B102" t="n">
-        <v>92004</v>
+        <v>91998</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12596,30 +12596,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573396</v>
+        <v>573326</v>
       </c>
       <c r="R102" t="n">
-        <v>6659037</v>
+        <v>6658892</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12709,7 +12709,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121680772</v>
+        <v>121680859</v>
       </c>
       <c r="B103" t="n">
         <v>92039</v>
@@ -12749,7 +12749,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573445</v>
+        <v>573519</v>
       </c>
       <c r="R103" t="n">
-        <v>6658922</v>
+        <v>6659018</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121681666</v>
+        <v>121680773</v>
       </c>
       <c r="B90" t="n">
-        <v>58061</v>
+        <v>91998</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11100,21 +11100,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103055</v>
+        <v>4362</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11122,9 +11122,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11133,13 +11133,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573385</v>
+        <v>573423</v>
       </c>
       <c r="R90" t="n">
-        <v>6658886</v>
+        <v>6658673</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11163,22 +11163,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121680773</v>
+        <v>121681666</v>
       </c>
       <c r="B91" t="n">
-        <v>91998</v>
+        <v>58061</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11225,21 +11225,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4362</v>
+        <v>103055</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11247,9 +11247,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573423</v>
+        <v>573385</v>
       </c>
       <c r="R91" t="n">
-        <v>6658673</v>
+        <v>6658886</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121680773</v>
+        <v>121680775</v>
       </c>
       <c r="B90" t="n">
-        <v>91998</v>
+        <v>90228</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11096,25 +11096,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11133,13 +11133,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573423</v>
+        <v>573420</v>
       </c>
       <c r="R90" t="n">
-        <v>6658673</v>
+        <v>6658800</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121681666</v>
+        <v>121680859</v>
       </c>
       <c r="B91" t="n">
-        <v>58061</v>
+        <v>92039</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11225,21 +11225,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103055</v>
+        <v>5966</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11247,9 +11247,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573385</v>
+        <v>573519</v>
       </c>
       <c r="R91" t="n">
-        <v>6658886</v>
+        <v>6659018</v>
       </c>
       <c r="S91" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121679577</v>
+        <v>121681091</v>
       </c>
       <c r="B92" t="n">
-        <v>57785</v>
+        <v>78642</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11346,25 +11346,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>103001</v>
+        <v>6434</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11372,9 +11372,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11383,13 +11383,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573462</v>
+        <v>573384</v>
       </c>
       <c r="R92" t="n">
-        <v>6658905</v>
+        <v>6658904</v>
       </c>
       <c r="S92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11459,10 +11459,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121681091</v>
+        <v>121679577</v>
       </c>
       <c r="B93" t="n">
-        <v>78642</v>
+        <v>57785</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11471,25 +11471,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6434</v>
+        <v>103001</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11497,9 +11497,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573384</v>
+        <v>573462</v>
       </c>
       <c r="R93" t="n">
-        <v>6658904</v>
+        <v>6658905</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11538,22 +11538,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121680774</v>
+        <v>121681090</v>
       </c>
       <c r="B94" t="n">
-        <v>92039</v>
+        <v>78642</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11596,25 +11596,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11633,13 +11633,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573413</v>
+        <v>573424</v>
       </c>
       <c r="R94" t="n">
-        <v>6658670</v>
+        <v>6659001</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11663,22 +11663,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680858</v>
+        <v>121680860</v>
       </c>
       <c r="B95" t="n">
-        <v>92004</v>
+        <v>91998</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,30 +11721,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11754,17 +11754,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573396</v>
+        <v>573326</v>
       </c>
       <c r="R95" t="n">
-        <v>6659037</v>
+        <v>6658892</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121681090</v>
+        <v>121680858</v>
       </c>
       <c r="B96" t="n">
-        <v>78642</v>
+        <v>92004</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11850,31 +11850,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573424</v>
+        <v>573396</v>
       </c>
       <c r="R96" t="n">
-        <v>6659001</v>
+        <v>6659037</v>
       </c>
       <c r="S96" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680772</v>
+        <v>121681666</v>
       </c>
       <c r="B97" t="n">
-        <v>92039</v>
+        <v>58061</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>103055</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11997,9 +11997,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12008,13 +12008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573445</v>
+        <v>573385</v>
       </c>
       <c r="R97" t="n">
-        <v>6658922</v>
+        <v>6658886</v>
       </c>
       <c r="S97" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12038,22 +12038,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680775</v>
+        <v>121680772</v>
       </c>
       <c r="B98" t="n">
-        <v>90228</v>
+        <v>92039</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12096,25 +12096,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573420</v>
+        <v>573445</v>
       </c>
       <c r="R98" t="n">
-        <v>6658800</v>
+        <v>6658922</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680776</v>
+        <v>121680761</v>
       </c>
       <c r="B99" t="n">
-        <v>92004</v>
+        <v>92039</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12221,25 +12221,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12249,22 +12249,22 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573374</v>
+        <v>573322</v>
       </c>
       <c r="R99" t="n">
-        <v>6658857</v>
+        <v>6658875</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12334,7 +12334,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680761</v>
+        <v>121680774</v>
       </c>
       <c r="B100" t="n">
         <v>92039</v>
@@ -12374,19 +12374,19 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573322</v>
+        <v>573413</v>
       </c>
       <c r="R100" t="n">
-        <v>6658875</v>
+        <v>6658670</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680860</v>
+        <v>121680776</v>
       </c>
       <c r="B102" t="n">
-        <v>91998</v>
+        <v>92004</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12596,25 +12596,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12624,19 +12624,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573326</v>
+        <v>573374</v>
       </c>
       <c r="R102" t="n">
-        <v>6658892</v>
+        <v>6658857</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121680859</v>
+        <v>121680773</v>
       </c>
       <c r="B103" t="n">
-        <v>92039</v>
+        <v>91998</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12758,10 +12758,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573519</v>
+        <v>573423</v>
       </c>
       <c r="R103" t="n">
-        <v>6659018</v>
+        <v>6658673</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121680775</v>
+        <v>121680761</v>
       </c>
       <c r="B90" t="n">
-        <v>90228</v>
+        <v>92053</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11096,25 +11096,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11124,22 +11124,22 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573420</v>
+        <v>573322</v>
       </c>
       <c r="R90" t="n">
-        <v>6658800</v>
+        <v>6658875</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11212,7 +11212,7 @@
         <v>121680859</v>
       </c>
       <c r="B91" t="n">
-        <v>92039</v>
+        <v>92053</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121681091</v>
+        <v>121681090</v>
       </c>
       <c r="B92" t="n">
-        <v>78642</v>
+        <v>78655</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11383,13 +11383,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573384</v>
+        <v>573424</v>
       </c>
       <c r="R92" t="n">
-        <v>6658904</v>
+        <v>6659001</v>
       </c>
       <c r="S92" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11462,7 +11462,7 @@
         <v>121679577</v>
       </c>
       <c r="B93" t="n">
-        <v>57785</v>
+        <v>57793</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121681090</v>
+        <v>121680774</v>
       </c>
       <c r="B94" t="n">
-        <v>78642</v>
+        <v>92053</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11596,25 +11596,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11633,13 +11633,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573424</v>
+        <v>573413</v>
       </c>
       <c r="R94" t="n">
-        <v>6659001</v>
+        <v>6658670</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11663,22 +11663,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680860</v>
+        <v>121680858</v>
       </c>
       <c r="B95" t="n">
-        <v>91998</v>
+        <v>92018</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,30 +11721,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11754,17 +11754,17 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573326</v>
+        <v>573396</v>
       </c>
       <c r="R95" t="n">
-        <v>6658892</v>
+        <v>6659037</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121680858</v>
+        <v>121681091</v>
       </c>
       <c r="B96" t="n">
-        <v>92004</v>
+        <v>78655</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11850,31 +11850,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573396</v>
+        <v>573384</v>
       </c>
       <c r="R96" t="n">
-        <v>6659037</v>
+        <v>6658904</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121681666</v>
+        <v>121680775</v>
       </c>
       <c r="B97" t="n">
-        <v>58061</v>
+        <v>90242</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11971,25 +11971,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103055</v>
+        <v>256703</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11997,9 +11997,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12008,10 +12008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573385</v>
+        <v>573420</v>
       </c>
       <c r="R97" t="n">
-        <v>6658886</v>
+        <v>6658800</v>
       </c>
       <c r="S97" t="n">
         <v>4</v>
@@ -12038,22 +12038,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680772</v>
+        <v>121681666</v>
       </c>
       <c r="B98" t="n">
-        <v>92039</v>
+        <v>58069</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12100,21 +12100,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5966</v>
+        <v>103055</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12122,9 +12122,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573445</v>
+        <v>573385</v>
       </c>
       <c r="R98" t="n">
-        <v>6658922</v>
+        <v>6658886</v>
       </c>
       <c r="S98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12163,22 +12163,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680761</v>
+        <v>121680860</v>
       </c>
       <c r="B99" t="n">
-        <v>92039</v>
+        <v>92012</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12225,21 +12225,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12258,13 +12258,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573322</v>
+        <v>573326</v>
       </c>
       <c r="R99" t="n">
-        <v>6658875</v>
+        <v>6658892</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12334,10 +12334,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680774</v>
+        <v>121680861</v>
       </c>
       <c r="B100" t="n">
-        <v>92039</v>
+        <v>92053</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12383,13 +12383,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573413</v>
+        <v>573378</v>
       </c>
       <c r="R100" t="n">
-        <v>6658670</v>
+        <v>6658802</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680861</v>
+        <v>121680773</v>
       </c>
       <c r="B101" t="n">
-        <v>92039</v>
+        <v>92012</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573378</v>
+        <v>573423</v>
       </c>
       <c r="R101" t="n">
-        <v>6658802</v>
+        <v>6658673</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12587,7 +12587,7 @@
         <v>121680776</v>
       </c>
       <c r="B102" t="n">
-        <v>92004</v>
+        <v>92018</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121680773</v>
+        <v>121680772</v>
       </c>
       <c r="B103" t="n">
-        <v>91998</v>
+        <v>92053</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573423</v>
+        <v>573445</v>
       </c>
       <c r="R103" t="n">
-        <v>6658673</v>
+        <v>6658922</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121680761</v>
+        <v>121681091</v>
       </c>
       <c r="B90" t="n">
-        <v>92053</v>
+        <v>78657</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11096,25 +11096,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11124,22 +11124,22 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573322</v>
+        <v>573384</v>
       </c>
       <c r="R90" t="n">
-        <v>6658875</v>
+        <v>6658904</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11163,22 +11163,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121680859</v>
+        <v>121679577</v>
       </c>
       <c r="B91" t="n">
-        <v>92053</v>
+        <v>57793</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11225,21 +11225,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>103001</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11247,9 +11247,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573519</v>
+        <v>573462</v>
       </c>
       <c r="R91" t="n">
-        <v>6659018</v>
+        <v>6658905</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121681090</v>
+        <v>121680761</v>
       </c>
       <c r="B92" t="n">
-        <v>78655</v>
+        <v>92055</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11346,25 +11346,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11374,22 +11374,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573424</v>
+        <v>573322</v>
       </c>
       <c r="R92" t="n">
-        <v>6659001</v>
+        <v>6658875</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11459,10 +11459,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121679577</v>
+        <v>121680775</v>
       </c>
       <c r="B93" t="n">
-        <v>57793</v>
+        <v>90244</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11471,25 +11471,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103001</v>
+        <v>256703</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11497,9 +11497,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573462</v>
+        <v>573420</v>
       </c>
       <c r="R93" t="n">
-        <v>6658905</v>
+        <v>6658800</v>
       </c>
       <c r="S93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11538,22 +11538,22 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121680774</v>
+        <v>121680859</v>
       </c>
       <c r="B94" t="n">
-        <v>92053</v>
+        <v>92055</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11633,10 +11633,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573413</v>
+        <v>573519</v>
       </c>
       <c r="R94" t="n">
-        <v>6658670</v>
+        <v>6659018</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680858</v>
+        <v>121680861</v>
       </c>
       <c r="B95" t="n">
-        <v>92018</v>
+        <v>92055</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,30 +11721,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -11758,13 +11758,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573396</v>
+        <v>573378</v>
       </c>
       <c r="R95" t="n">
-        <v>6659037</v>
+        <v>6658802</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121681091</v>
+        <v>121680773</v>
       </c>
       <c r="B96" t="n">
-        <v>78655</v>
+        <v>92014</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11846,25 +11846,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6434</v>
+        <v>4362</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573384</v>
+        <v>573423</v>
       </c>
       <c r="R96" t="n">
-        <v>6658904</v>
+        <v>6658673</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680775</v>
+        <v>121681666</v>
       </c>
       <c r="B97" t="n">
-        <v>90242</v>
+        <v>58069</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11971,25 +11971,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>256703</v>
+        <v>103055</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11997,9 +11997,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12008,10 +12008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573420</v>
+        <v>573385</v>
       </c>
       <c r="R97" t="n">
-        <v>6658800</v>
+        <v>6658886</v>
       </c>
       <c r="S97" t="n">
         <v>4</v>
@@ -12038,22 +12038,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121681666</v>
+        <v>121680860</v>
       </c>
       <c r="B98" t="n">
-        <v>58069</v>
+        <v>92014</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12100,21 +12100,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103055</v>
+        <v>4362</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12122,21 +12122,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573385</v>
+        <v>573326</v>
       </c>
       <c r="R98" t="n">
-        <v>6658886</v>
+        <v>6658892</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -12163,22 +12163,22 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680860</v>
+        <v>121680772</v>
       </c>
       <c r="B99" t="n">
-        <v>92012</v>
+        <v>92055</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12225,21 +12225,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -12249,22 +12249,22 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573326</v>
+        <v>573445</v>
       </c>
       <c r="R99" t="n">
-        <v>6658892</v>
+        <v>6658922</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12334,10 +12334,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680861</v>
+        <v>121680776</v>
       </c>
       <c r="B100" t="n">
-        <v>92053</v>
+        <v>92020</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12346,25 +12346,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12383,10 +12383,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573378</v>
+        <v>573374</v>
       </c>
       <c r="R100" t="n">
-        <v>6658802</v>
+        <v>6658857</v>
       </c>
       <c r="S100" t="n">
         <v>4</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680773</v>
+        <v>121680774</v>
       </c>
       <c r="B101" t="n">
-        <v>92012</v>
+        <v>92055</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12508,10 +12508,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573423</v>
+        <v>573413</v>
       </c>
       <c r="R101" t="n">
-        <v>6658673</v>
+        <v>6658670</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12553,7 +12553,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680776</v>
+        <v>121680858</v>
       </c>
       <c r="B102" t="n">
-        <v>92018</v>
+        <v>92020</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12619,12 +12619,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573374</v>
+        <v>573396</v>
       </c>
       <c r="R102" t="n">
-        <v>6658857</v>
+        <v>6659037</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121680772</v>
+        <v>121681090</v>
       </c>
       <c r="B103" t="n">
-        <v>92053</v>
+        <v>78657</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12721,25 +12721,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573445</v>
+        <v>573424</v>
       </c>
       <c r="R103" t="n">
-        <v>6658922</v>
+        <v>6659001</v>
       </c>
       <c r="S103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD103" t="b">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121681091</v>
+        <v>121680761</v>
       </c>
       <c r="B90" t="n">
-        <v>78657</v>
+        <v>92056</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11096,25 +11096,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -11124,22 +11124,22 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573384</v>
+        <v>573322</v>
       </c>
       <c r="R90" t="n">
-        <v>6658904</v>
+        <v>6658875</v>
       </c>
       <c r="S90" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11163,22 +11163,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11198,7 +11198,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121679577</v>
+        <v>121681090</v>
       </c>
       <c r="B91" t="n">
-        <v>57793</v>
+        <v>78658</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11221,25 +11221,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>103001</v>
+        <v>6434</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11247,9 +11247,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573462</v>
+        <v>573424</v>
       </c>
       <c r="R91" t="n">
-        <v>6658905</v>
+        <v>6659001</v>
       </c>
       <c r="S91" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121680761</v>
+        <v>121680859</v>
       </c>
       <c r="B92" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11379,14 +11379,14 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573322</v>
+        <v>573519</v>
       </c>
       <c r="R92" t="n">
-        <v>6658875</v>
+        <v>6659018</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11418,7 +11418,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11459,10 +11459,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121680775</v>
+        <v>121680772</v>
       </c>
       <c r="B93" t="n">
-        <v>90244</v>
+        <v>92056</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11471,25 +11471,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573420</v>
+        <v>573445</v>
       </c>
       <c r="R93" t="n">
-        <v>6658800</v>
+        <v>6658922</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121680859</v>
+        <v>121681666</v>
       </c>
       <c r="B94" t="n">
-        <v>92055</v>
+        <v>58069</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11600,21 +11600,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5966</v>
+        <v>103055</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11622,9 +11622,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11633,13 +11633,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573519</v>
+        <v>573385</v>
       </c>
       <c r="R94" t="n">
-        <v>6659018</v>
+        <v>6658886</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11663,22 +11663,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680861</v>
+        <v>121680776</v>
       </c>
       <c r="B95" t="n">
-        <v>92055</v>
+        <v>92021</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,25 +11721,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573378</v>
+        <v>573374</v>
       </c>
       <c r="R95" t="n">
-        <v>6658802</v>
+        <v>6658857</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -11793,7 +11793,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121680773</v>
+        <v>121681091</v>
       </c>
       <c r="B96" t="n">
-        <v>92014</v>
+        <v>78658</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11846,25 +11846,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573423</v>
+        <v>573384</v>
       </c>
       <c r="R96" t="n">
-        <v>6658673</v>
+        <v>6658904</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121681666</v>
+        <v>121680773</v>
       </c>
       <c r="B97" t="n">
-        <v>58069</v>
+        <v>92015</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103055</v>
+        <v>4362</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11997,9 +11997,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12008,13 +12008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573385</v>
+        <v>573423</v>
       </c>
       <c r="R97" t="n">
-        <v>6658886</v>
+        <v>6658673</v>
       </c>
       <c r="S97" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12038,22 +12038,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680860</v>
+        <v>121680775</v>
       </c>
       <c r="B98" t="n">
-        <v>92014</v>
+        <v>90245</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12096,25 +12096,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4362</v>
+        <v>256703</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -12124,19 +12124,19 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573326</v>
+        <v>573420</v>
       </c>
       <c r="R98" t="n">
-        <v>6658892</v>
+        <v>6658800</v>
       </c>
       <c r="S98" t="n">
         <v>4</v>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680772</v>
+        <v>121680774</v>
       </c>
       <c r="B99" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12258,13 +12258,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573445</v>
+        <v>573413</v>
       </c>
       <c r="R99" t="n">
-        <v>6658922</v>
+        <v>6658670</v>
       </c>
       <c r="S99" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12334,10 +12334,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680776</v>
+        <v>121680858</v>
       </c>
       <c r="B100" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12369,12 +12369,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -12383,13 +12383,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573374</v>
+        <v>573396</v>
       </c>
       <c r="R100" t="n">
-        <v>6658857</v>
+        <v>6659037</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680774</v>
+        <v>121679577</v>
       </c>
       <c r="B101" t="n">
-        <v>92055</v>
+        <v>57793</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>103001</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12497,9 +12497,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>mycel</t>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573413</v>
+        <v>573462</v>
       </c>
       <c r="R101" t="n">
-        <v>6658670</v>
+        <v>6658905</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12538,22 +12538,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680858</v>
+        <v>121680860</v>
       </c>
       <c r="B102" t="n">
-        <v>92020</v>
+        <v>92015</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12596,30 +12596,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12629,17 +12629,17 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573396</v>
+        <v>573326</v>
       </c>
       <c r="R102" t="n">
-        <v>6659037</v>
+        <v>6658892</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121681090</v>
+        <v>121680861</v>
       </c>
       <c r="B103" t="n">
-        <v>78657</v>
+        <v>92056</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12721,25 +12721,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573424</v>
+        <v>573378</v>
       </c>
       <c r="R103" t="n">
-        <v>6659001</v>
+        <v>6658802</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121681090</v>
+        <v>121680859</v>
       </c>
       <c r="B91" t="n">
-        <v>78658</v>
+        <v>92056</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11221,25 +11221,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11249,7 +11249,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -11258,13 +11258,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573424</v>
+        <v>573519</v>
       </c>
       <c r="R91" t="n">
-        <v>6659001</v>
+        <v>6659018</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11288,22 +11288,22 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11323,7 +11323,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121680859</v>
+        <v>121681090</v>
       </c>
       <c r="B92" t="n">
-        <v>92056</v>
+        <v>78658</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11346,25 +11346,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -11383,13 +11383,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573519</v>
+        <v>573424</v>
       </c>
       <c r="R92" t="n">
-        <v>6659018</v>
+        <v>6659001</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121681666</v>
+        <v>121680776</v>
       </c>
       <c r="B94" t="n">
-        <v>58069</v>
+        <v>92021</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11596,25 +11596,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>103055</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11622,9 +11622,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -11633,10 +11633,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573385</v>
+        <v>573374</v>
       </c>
       <c r="R94" t="n">
-        <v>6658886</v>
+        <v>6658857</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
@@ -11663,22 +11663,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121680776</v>
+        <v>121681091</v>
       </c>
       <c r="B95" t="n">
-        <v>92021</v>
+        <v>78658</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11725,21 +11725,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6434</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11758,13 +11758,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573374</v>
+        <v>573384</v>
       </c>
       <c r="R95" t="n">
-        <v>6658857</v>
+        <v>6658904</v>
       </c>
       <c r="S95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11788,22 +11788,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121681091</v>
+        <v>121680775</v>
       </c>
       <c r="B96" t="n">
-        <v>78658</v>
+        <v>90245</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11850,21 +11850,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6434</v>
+        <v>256703</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573384</v>
+        <v>573420</v>
       </c>
       <c r="R96" t="n">
-        <v>6658904</v>
+        <v>6658800</v>
       </c>
       <c r="S96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11913,22 +11913,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680775</v>
+        <v>121680858</v>
       </c>
       <c r="B98" t="n">
-        <v>90245</v>
+        <v>92021</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12100,31 +12100,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573420</v>
+        <v>573396</v>
       </c>
       <c r="R98" t="n">
-        <v>6658800</v>
+        <v>6659037</v>
       </c>
       <c r="S98" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12334,10 +12334,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680858</v>
+        <v>121680860</v>
       </c>
       <c r="B100" t="n">
-        <v>92021</v>
+        <v>92015</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12346,30 +12346,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12379,17 +12379,17 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573396</v>
+        <v>573326</v>
       </c>
       <c r="R100" t="n">
-        <v>6659037</v>
+        <v>6658892</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121679577</v>
+        <v>121680861</v>
       </c>
       <c r="B101" t="n">
-        <v>57793</v>
+        <v>92056</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12475,21 +12475,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103001</v>
+        <v>5966</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12497,9 +12497,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573462</v>
+        <v>573378</v>
       </c>
       <c r="R101" t="n">
-        <v>6658905</v>
+        <v>6658802</v>
       </c>
       <c r="S101" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12538,22 +12538,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12584,14 +12584,14 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121680860</v>
+        <v>121681666</v>
       </c>
       <c r="B102" t="n">
-        <v>92015</v>
+        <v>58069</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4362</v>
+        <v>103055</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12622,21 +12622,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573326</v>
+        <v>573385</v>
       </c>
       <c r="R102" t="n">
-        <v>6658892</v>
+        <v>6658886</v>
       </c>
       <c r="S102" t="n">
         <v>4</v>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,14 +12709,14 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121680861</v>
+        <v>121679577</v>
       </c>
       <c r="B103" t="n">
-        <v>92056</v>
+        <v>57793</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5966</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12747,9 +12747,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573378</v>
+        <v>573462</v>
       </c>
       <c r="R103" t="n">
-        <v>6658802</v>
+        <v>6658905</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -11084,10 +11084,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121680761</v>
+        <v>121680858</v>
       </c>
       <c r="B90" t="n">
-        <v>92056</v>
+        <v>92030</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11096,30 +11096,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11129,14 +11129,14 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>573322</v>
+        <v>573396</v>
       </c>
       <c r="R90" t="n">
-        <v>6658875</v>
+        <v>6659037</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11168,7 +11168,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11209,10 +11209,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121680859</v>
+        <v>121680860</v>
       </c>
       <c r="B91" t="n">
-        <v>92056</v>
+        <v>92024</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11225,21 +11225,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5966</v>
+        <v>4362</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -11254,17 +11254,17 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>573519</v>
+        <v>573326</v>
       </c>
       <c r="R91" t="n">
-        <v>6659018</v>
+        <v>6658892</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11303,7 +11303,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11334,10 +11334,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121681090</v>
+        <v>121680761</v>
       </c>
       <c r="B92" t="n">
-        <v>78658</v>
+        <v>92065</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11346,25 +11346,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -11374,22 +11374,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Långheden, Vstm</t>
+          <t>Stormossen, Vstm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>573424</v>
+        <v>573322</v>
       </c>
       <c r="R92" t="n">
-        <v>6659001</v>
+        <v>6658875</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11413,22 +11413,22 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11459,10 +11459,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121680772</v>
+        <v>121680775</v>
       </c>
       <c r="B93" t="n">
-        <v>92056</v>
+        <v>90254</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11471,25 +11471,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5966</v>
+        <v>256703</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -11508,13 +11508,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>573445</v>
+        <v>573420</v>
       </c>
       <c r="R93" t="n">
-        <v>6658922</v>
+        <v>6658800</v>
       </c>
       <c r="S93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11553,7 +11553,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11584,10 +11584,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121680776</v>
+        <v>121680773</v>
       </c>
       <c r="B94" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11596,25 +11596,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -11633,13 +11633,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>573374</v>
+        <v>573423</v>
       </c>
       <c r="R94" t="n">
-        <v>6658857</v>
+        <v>6658673</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121681091</v>
+        <v>121680772</v>
       </c>
       <c r="B95" t="n">
-        <v>78658</v>
+        <v>92065</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11721,25 +11721,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11749,7 +11749,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -11758,10 +11758,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>573384</v>
+        <v>573445</v>
       </c>
       <c r="R95" t="n">
-        <v>6658904</v>
+        <v>6658922</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -11788,22 +11788,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121680775</v>
+        <v>121680774</v>
       </c>
       <c r="B96" t="n">
-        <v>90245</v>
+        <v>92065</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11846,25 +11846,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>256703</v>
+        <v>5966</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11883,13 +11883,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>573420</v>
+        <v>573413</v>
       </c>
       <c r="R96" t="n">
-        <v>6658800</v>
+        <v>6658670</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11918,7 +11918,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11959,10 +11959,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121680773</v>
+        <v>121681091</v>
       </c>
       <c r="B97" t="n">
-        <v>92015</v>
+        <v>78665</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11971,25 +11971,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4362</v>
+        <v>6434</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -12008,13 +12008,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>573423</v>
+        <v>573384</v>
       </c>
       <c r="R97" t="n">
-        <v>6658673</v>
+        <v>6658904</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12038,22 +12038,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12084,10 +12084,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121680858</v>
+        <v>121680861</v>
       </c>
       <c r="B98" t="n">
-        <v>92021</v>
+        <v>92065</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -12096,30 +12096,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
@@ -12133,13 +12133,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>573396</v>
+        <v>573378</v>
       </c>
       <c r="R98" t="n">
-        <v>6659037</v>
+        <v>6658802</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12178,7 +12178,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12209,10 +12209,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121680774</v>
+        <v>121680859</v>
       </c>
       <c r="B99" t="n">
-        <v>92056</v>
+        <v>92065</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>573413</v>
+        <v>573519</v>
       </c>
       <c r="R99" t="n">
-        <v>6658670</v>
+        <v>6659018</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12293,7 +12293,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12303,7 +12303,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12334,10 +12334,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121680860</v>
+        <v>121680776</v>
       </c>
       <c r="B100" t="n">
-        <v>92015</v>
+        <v>92030</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12346,25 +12346,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -12374,19 +12374,19 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stormossen, Vstm</t>
+          <t>Långheden, Vstm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>573326</v>
+        <v>573374</v>
       </c>
       <c r="R100" t="n">
-        <v>6658892</v>
+        <v>6658857</v>
       </c>
       <c r="S100" t="n">
         <v>4</v>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12459,10 +12459,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121680861</v>
+        <v>121681090</v>
       </c>
       <c r="B101" t="n">
-        <v>92056</v>
+        <v>78665</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12471,25 +12471,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5966</v>
+        <v>6434</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -12499,7 +12499,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -12508,13 +12508,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>573378</v>
+        <v>573424</v>
       </c>
       <c r="R101" t="n">
-        <v>6658802</v>
+        <v>6659001</v>
       </c>
       <c r="S101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12538,22 +12538,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2023-10-23</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121681666</v>
+        <v>121679577</v>
       </c>
       <c r="B102" t="n">
-        <v>58069</v>
+        <v>57797</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573385</v>
+        <v>573462</v>
       </c>
       <c r="R102" t="n">
-        <v>6658886</v>
+        <v>6658905</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B103" t="n">
-        <v>57793</v>
+        <v>58073</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R103" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B102" t="n">
-        <v>57797</v>
+        <v>58077</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R102" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121681666</v>
+        <v>121679577</v>
       </c>
       <c r="B103" t="n">
-        <v>58073</v>
+        <v>57801</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573385</v>
+        <v>573462</v>
       </c>
       <c r="R103" t="n">
-        <v>6658886</v>
+        <v>6658905</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121681666</v>
+        <v>121679577</v>
       </c>
       <c r="B102" t="n">
-        <v>58077</v>
+        <v>57803</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573385</v>
+        <v>573462</v>
       </c>
       <c r="R102" t="n">
-        <v>6658886</v>
+        <v>6658905</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B103" t="n">
-        <v>57801</v>
+        <v>58079</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R103" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B102" t="n">
-        <v>57803</v>
+        <v>58079</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R102" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121681666</v>
+        <v>121679577</v>
       </c>
       <c r="B103" t="n">
-        <v>58079</v>
+        <v>57803</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573385</v>
+        <v>573462</v>
       </c>
       <c r="R103" t="n">
-        <v>6658886</v>
+        <v>6658905</v>
       </c>
       <c r="S103" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121681666</v>
+        <v>121679577</v>
       </c>
       <c r="B102" t="n">
-        <v>58079</v>
+        <v>57803</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103055</v>
+        <v>103001</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12633,13 +12633,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573385</v>
+        <v>573462</v>
       </c>
       <c r="R102" t="n">
-        <v>6658886</v>
+        <v>6658905</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12663,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12709,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B103" t="n">
-        <v>57803</v>
+        <v>58079</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12725,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
+        <v>103055</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12758,13 +12758,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R103" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12788,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12823,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -12587,7 +12587,7 @@
         <v>121681666</v>
       </c>
       <c r="B102" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>121679577</v>
       </c>
       <c r="B103" t="n">
-        <v>57803</v>
+        <v>57808</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -12584,10 +12584,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121681666</v>
+        <v>121679577</v>
       </c>
       <c r="B102" t="n">
-        <v>58084</v>
+        <v>57808</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12600,21 +12600,16 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
+        <v>103001</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -12633,13 +12628,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>573385</v>
+        <v>573462</v>
       </c>
       <c r="R102" t="n">
-        <v>6658886</v>
+        <v>6658905</v>
       </c>
       <c r="S102" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12663,22 +12658,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-04-24</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>06:59</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12698,7 +12693,7 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Jannik Jansons</t>
+          <t>Jake Bull</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12709,10 +12704,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121679577</v>
+        <v>121681666</v>
       </c>
       <c r="B103" t="n">
-        <v>57808</v>
+        <v>58084</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12725,21 +12720,16 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>103001</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Rödvingetrast</t>
-        </is>
+        <v>103055</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -12758,13 +12748,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>573462</v>
+        <v>573385</v>
       </c>
       <c r="R103" t="n">
-        <v>6658905</v>
+        <v>6658886</v>
       </c>
       <c r="S103" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12788,22 +12778,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>06:59</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12823,7 +12813,7 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Jake Bull</t>
+          <t>Jannik Jansons</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">

--- a/artfynd/A 44181-2023 artfynd.xlsx
+++ b/artfynd/A 44181-2023 artfynd.xlsx
@@ -12587,7 +12587,7 @@
         <v>121679577</v>
       </c>
       <c r="B102" t="n">
-        <v>57808</v>
+        <v>57812</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12601,6 +12601,11 @@
       </c>
       <c r="E102" t="n">
         <v>103001</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -12707,7 +12712,7 @@
         <v>121681666</v>
       </c>
       <c r="B103" t="n">
-        <v>58084</v>
+        <v>58088</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12721,6 +12726,11 @@
       </c>
       <c r="E103" t="n">
         <v>103055</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
